--- a/Normalisasi_SalesDB_Bagas.xlsx
+++ b/Normalisasi_SalesDB_Bagas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bagas\OneDrive\Desktop\Maganghub X MII\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC87072-FB94-4A4C-A5F1-FB6B31E65CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F3C872-455C-4302-8566-3BBF338C8E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,17 @@
     <sheet name="4_3NF" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -47,8 +58,32 @@
 </comments>
 </file>
 
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Trainer</author>
+  </authors>
+  <commentList>
+    <comment ref="G13" authorId="0" shapeId="0" xr:uid="{5BC63969-EDE8-433A-8A02-753ABC4FC765}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="11"/>
+            <color theme="1"/>
+            <rFont val="Calibri"/>
+            <family val="2"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>Nilai tertulis di faktur asli (data sumber). Nilai ini dipertahankan sampai 3NF, lalu di sheet 4_3NF dibuktikan bahwa nilainya bisa dihitung ulang dari Qty × Harga.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="263" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="135">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -402,6 +437,12 @@
     <t>Sulit membuat laporan</t>
   </si>
   <si>
+    <t>No Faktur (PK/FK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (PK/FK)</t>
+  </si>
+  <si>
     <t>P001</t>
   </si>
   <si>
@@ -454,6 +495,33 @@
   </si>
   <si>
     <t>Memecah sel yang memiliki nilai jamak alasannya Memenuhi syarat 1NF, yaitu memastikan setiap sel berisi nilai atomik</t>
+  </si>
+  <si>
+    <t>Tabel Faktur</t>
+  </si>
+  <si>
+    <t>Tabel Produk</t>
+  </si>
+  <si>
+    <t>No Faktur (PK)</t>
+  </si>
+  <si>
+    <t>Kode Produk (PK)</t>
+  </si>
+  <si>
+    <t>Tabel Detail Faktur</t>
+  </si>
+  <si>
+    <t>No Faktur, Kode Produk, (No faktur, kode produk)</t>
+  </si>
+  <si>
+    <t>No faktur : tanggal, kode pelanggan, nama pelanggan, email, kota. Kode Produk : Nama Produk, Kode Kategori, Nama Kategori. (No faktur, kode produk): Qty, Harga Satuan.</t>
+  </si>
+  <si>
+    <t>Memecah 1NF menjadi 3 tabel dengan menghilangkan partial depedency</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tabel Pelanggan </t>
   </si>
 </sst>
 </file>
@@ -461,11 +529,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="3">
-    <numFmt numFmtId="165" formatCode="dd\-mm\-yyyy"/>
-    <numFmt numFmtId="170" formatCode="[$Rp-421]#,##0.00"/>
-    <numFmt numFmtId="172" formatCode="[$Rp-421]#,##0"/>
+    <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy"/>
+    <numFmt numFmtId="165" formatCode="[$Rp-421]#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="[$Rp-421]#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -544,8 +612,28 @@
       <name val="Arial"/>
       <family val="2"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -575,6 +663,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -611,7 +705,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -629,7 +723,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -640,7 +734,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top"/>
@@ -659,9 +753,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -670,17 +761,40 @@
     <xf numFmtId="0" fontId="13" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="170" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="170" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1181,9 +1295,9 @@
       <c r="M4" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="O4" s="27"/>
-      <c r="P4" s="27"/>
-      <c r="Q4" s="27"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="26"/>
+      <c r="Q4" s="26"/>
     </row>
     <row r="5" spans="1:17" ht="48" customHeight="1">
       <c r="A5" s="12" t="s">
@@ -1204,7 +1318,7 @@
       <c r="F5" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="G5" s="28" t="s">
+      <c r="G5" s="27" t="s">
         <v>40</v>
       </c>
       <c r="H5" s="12" t="s">
@@ -1225,9 +1339,9 @@
       <c r="M5" s="14">
         <v>2150000</v>
       </c>
-      <c r="O5" s="26"/>
-      <c r="P5" s="25"/>
-      <c r="Q5" s="25"/>
+      <c r="O5" s="25"/>
+      <c r="P5" s="42"/>
+      <c r="Q5" s="42"/>
     </row>
     <row r="6" spans="1:17" ht="48" customHeight="1">
       <c r="A6" s="12" t="s">
@@ -1269,9 +1383,9 @@
       <c r="M6" s="14">
         <v>900000</v>
       </c>
-      <c r="O6" s="26"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
+      <c r="O6" s="25"/>
+      <c r="P6" s="26"/>
+      <c r="Q6" s="26"/>
     </row>
     <row r="7" spans="1:17" ht="48" customHeight="1">
       <c r="A7" s="12" t="s">
@@ -1313,9 +1427,9 @@
       <c r="M7" s="14">
         <v>1050000</v>
       </c>
-      <c r="O7" s="26"/>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="27"/>
+      <c r="O7" s="25"/>
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
     </row>
     <row r="8" spans="1:17" ht="48" customHeight="1">
       <c r="A8" s="12" t="s">
@@ -1357,9 +1471,9 @@
       <c r="M8" s="14">
         <v>346000</v>
       </c>
-      <c r="O8" s="26"/>
-      <c r="P8" s="27"/>
-      <c r="Q8" s="27"/>
+      <c r="O8" s="25"/>
+      <c r="P8" s="26"/>
+      <c r="Q8" s="26"/>
     </row>
     <row r="9" spans="1:17" ht="48" customHeight="1">
       <c r="A9" s="12" t="s">
@@ -1401,9 +1515,9 @@
       <c r="M9" s="14">
         <v>548000</v>
       </c>
-      <c r="O9" s="26"/>
-      <c r="P9" s="27"/>
-      <c r="Q9" s="27"/>
+      <c r="O9" s="25"/>
+      <c r="P9" s="26"/>
+      <c r="Q9" s="26"/>
     </row>
     <row r="10" spans="1:17" ht="48" customHeight="1">
       <c r="A10" s="12" t="s">
@@ -1445,15 +1559,15 @@
       <c r="M10" s="14">
         <v>4450000</v>
       </c>
-      <c r="O10" s="26"/>
-      <c r="P10" s="27"/>
-      <c r="Q10" s="27"/>
+      <c r="O10" s="25"/>
+      <c r="P10" s="26"/>
+      <c r="Q10" s="26"/>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="19" t="s">
+      <c r="A12" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="19"/>
+      <c r="B12" s="41"/>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
@@ -1699,12 +1813,12 @@
     <col min="4" max="4" width="17.88671875" customWidth="1"/>
     <col min="5" max="5" width="20" customWidth="1"/>
     <col min="6" max="6" width="14.77734375" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="18.109375" customWidth="1"/>
     <col min="9" max="9" width="14.6640625" customWidth="1"/>
     <col min="10" max="10" width="17.88671875" customWidth="1"/>
     <col min="11" max="11" width="8.88671875" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" style="32" customWidth="1"/>
+    <col min="12" max="12" width="14.44140625" style="31" customWidth="1"/>
     <col min="13" max="13" width="16.5546875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1733,7 +1847,7 @@
         <v>16</v>
       </c>
       <c r="B6" s="16" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
@@ -1743,10 +1857,10 @@
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="30" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="17" t="s">
+      <c r="B7" s="29" t="s">
+        <v>124</v>
+      </c>
+      <c r="C7" s="35" t="s">
         <v>93</v>
       </c>
     </row>
@@ -1754,8 +1868,8 @@
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="31" t="s">
-        <v>123</v>
+      <c r="B8" s="30" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="10" spans="1:13">
@@ -1765,7 +1879,7 @@
       <c r="B10" s="21"/>
     </row>
     <row r="11" spans="1:13" ht="27.6">
-      <c r="A11" s="29" t="s">
+      <c r="A11" s="28" t="s">
         <v>22</v>
       </c>
       <c r="B11" s="11" t="s">
@@ -1783,7 +1897,7 @@
       <c r="F11" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G11" s="11" t="s">
+      <c r="G11" s="28" t="s">
         <v>28</v>
       </c>
       <c r="H11" s="11" t="s">
@@ -1798,7 +1912,7 @@
       <c r="K11" s="11" t="s">
         <v>32</v>
       </c>
-      <c r="L11" s="33" t="s">
+      <c r="L11" s="32" t="s">
         <v>33</v>
       </c>
       <c r="M11" s="11" t="s">
@@ -1825,10 +1939,10 @@
         <v>39</v>
       </c>
       <c r="G12" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I12" t="s">
         <v>64</v>
@@ -1839,11 +1953,11 @@
       <c r="K12">
         <v>1</v>
       </c>
-      <c r="L12" s="32" t="s">
-        <v>108</v>
-      </c>
-      <c r="M12" s="32" t="s">
-        <v>108</v>
+      <c r="L12" s="31" t="s">
+        <v>110</v>
+      </c>
+      <c r="M12" s="31" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="13" spans="1:13">
@@ -1866,24 +1980,24 @@
         <v>39</v>
       </c>
       <c r="G13" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H13" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I13" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J13" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K13">
         <v>2</v>
       </c>
-      <c r="L13" s="34">
+      <c r="L13" s="33">
         <v>150000</v>
       </c>
-      <c r="M13" s="34">
+      <c r="M13" s="33">
         <f>SUM(L13*K13)</f>
         <v>300000</v>
       </c>
@@ -1908,24 +2022,24 @@
         <v>50</v>
       </c>
       <c r="G14" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" t="s">
         <v>113</v>
       </c>
-      <c r="H14" t="s">
+      <c r="J14" t="s">
         <v>114</v>
-      </c>
-      <c r="I14" t="s">
-        <v>111</v>
-      </c>
-      <c r="J14" t="s">
-        <v>112</v>
       </c>
       <c r="K14">
         <v>1</v>
       </c>
-      <c r="L14" s="34">
+      <c r="L14" s="33">
         <v>750000</v>
       </c>
-      <c r="M14" s="34">
+      <c r="M14" s="33">
         <f t="shared" ref="M14:M23" si="0">SUM(L14*K14)</f>
         <v>750000</v>
       </c>
@@ -1950,24 +2064,24 @@
         <v>50</v>
       </c>
       <c r="G15" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="H15" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="I15" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="J15" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="K15">
         <v>1</v>
       </c>
-      <c r="L15" s="34">
+      <c r="L15" s="33">
         <v>150000</v>
       </c>
-      <c r="M15" s="34">
+      <c r="M15" s="33">
         <f t="shared" si="0"/>
         <v>150000</v>
       </c>
@@ -2006,10 +2120,10 @@
       <c r="K16">
         <v>3</v>
       </c>
-      <c r="L16" s="34">
+      <c r="L16" s="33">
         <v>350000</v>
       </c>
-      <c r="M16" s="34">
+      <c r="M16" s="33">
         <f t="shared" si="0"/>
         <v>1050000</v>
       </c>
@@ -2034,24 +2148,24 @@
         <v>39</v>
       </c>
       <c r="G17" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H17" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I17" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J17" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K17">
         <v>10</v>
       </c>
-      <c r="L17" s="34">
+      <c r="L17" s="33">
         <v>25000</v>
       </c>
-      <c r="M17" s="34">
+      <c r="M17" s="33">
         <f t="shared" si="0"/>
         <v>250000</v>
       </c>
@@ -2076,24 +2190,24 @@
         <v>39</v>
       </c>
       <c r="G18" t="s">
+        <v>121</v>
+      </c>
+      <c r="H18" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" t="s">
         <v>119</v>
       </c>
-      <c r="H18" t="s">
+      <c r="J18" t="s">
         <v>120</v>
-      </c>
-      <c r="I18" t="s">
-        <v>117</v>
-      </c>
-      <c r="J18" t="s">
-        <v>118</v>
       </c>
       <c r="K18">
         <v>2</v>
       </c>
-      <c r="L18" s="34">
+      <c r="L18" s="33">
         <v>48000</v>
       </c>
-      <c r="M18" s="34">
+      <c r="M18" s="33">
         <f t="shared" si="0"/>
         <v>96000</v>
       </c>
@@ -2132,10 +2246,10 @@
       <c r="K19">
         <v>1</v>
       </c>
-      <c r="L19" s="34">
+      <c r="L19" s="33">
         <v>375000</v>
       </c>
-      <c r="M19" s="34">
+      <c r="M19" s="33">
         <f t="shared" si="0"/>
         <v>375000</v>
       </c>
@@ -2160,24 +2274,24 @@
         <v>50</v>
       </c>
       <c r="G20" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="H20" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="I20" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="J20" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="K20">
         <v>5</v>
       </c>
-      <c r="L20" s="34">
+      <c r="L20" s="33">
         <v>25000</v>
       </c>
-      <c r="M20" s="34">
+      <c r="M20" s="33">
         <f t="shared" si="0"/>
         <v>125000</v>
       </c>
@@ -2202,24 +2316,24 @@
         <v>50</v>
       </c>
       <c r="G21" t="s">
+        <v>121</v>
+      </c>
+      <c r="H21" t="s">
+        <v>122</v>
+      </c>
+      <c r="I21" t="s">
         <v>119</v>
       </c>
-      <c r="H21" t="s">
+      <c r="J21" t="s">
         <v>120</v>
-      </c>
-      <c r="I21" t="s">
-        <v>117</v>
-      </c>
-      <c r="J21" t="s">
-        <v>118</v>
       </c>
       <c r="K21">
         <v>1</v>
       </c>
-      <c r="L21" s="34">
+      <c r="L21" s="33">
         <v>48000</v>
       </c>
-      <c r="M21" s="34">
+      <c r="M21" s="33">
         <f t="shared" si="0"/>
         <v>48000</v>
       </c>
@@ -2244,10 +2358,10 @@
         <v>61</v>
       </c>
       <c r="G22" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H22" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="I22" t="s">
         <v>64</v>
@@ -2258,10 +2372,10 @@
       <c r="K22">
         <v>2</v>
       </c>
-      <c r="L22" s="34">
+      <c r="L22" s="33">
         <v>1850000</v>
       </c>
-      <c r="M22" s="34">
+      <c r="M22" s="33">
         <f t="shared" si="0"/>
         <v>3700000</v>
       </c>
@@ -2286,24 +2400,24 @@
         <v>61</v>
       </c>
       <c r="G23" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" t="s">
         <v>113</v>
       </c>
-      <c r="H23" t="s">
+      <c r="J23" t="s">
         <v>114</v>
-      </c>
-      <c r="I23" t="s">
-        <v>111</v>
-      </c>
-      <c r="J23" t="s">
-        <v>112</v>
       </c>
       <c r="K23">
         <v>1</v>
       </c>
-      <c r="L23" s="34">
+      <c r="L23" s="33">
         <v>750000</v>
       </c>
-      <c r="M23" s="34">
+      <c r="M23" s="33">
         <f t="shared" si="0"/>
         <v>750000</v>
       </c>
@@ -2314,36 +2428,555 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:C11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G42"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="1" max="1" width="36.77734375" customWidth="1"/>
+    <col min="2" max="2" width="60" customWidth="1"/>
+    <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="21.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="12.21875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" ht="16.8">
+      <c r="A1" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="3" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="36" customHeight="1">
+      <c r="A6" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="51.6" customHeight="1">
+      <c r="A7" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="B7" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" s="17" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" ht="36" customHeight="1">
+      <c r="A8" s="15" t="s">
+        <v>94</v>
+      </c>
+      <c r="B8" s="16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="34" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="37" t="s">
+        <v>128</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="38"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="13">
+        <v>46266</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G13" s="14"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B14" s="13">
+        <v>46275</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G14" s="14"/>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" s="13">
+        <v>46277</v>
+      </c>
+      <c r="C15" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="14"/>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="13">
+        <v>46280</v>
+      </c>
+      <c r="C16" s="36" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="F16" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="G16" s="14"/>
+    </row>
+    <row r="17" spans="1:7">
+      <c r="A17" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B17" s="13">
+        <v>46283</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="E17" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="12" t="s">
+        <v>50</v>
+      </c>
+      <c r="G17" s="14"/>
+    </row>
+    <row r="18" spans="1:7">
+      <c r="A18" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" s="13">
+        <v>46285</v>
+      </c>
+      <c r="C18" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>59</v>
+      </c>
+      <c r="E18" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="F18" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="G18" s="14"/>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20" s="34" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C21" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="D21" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22" t="s">
+        <v>108</v>
+      </c>
+      <c r="B22" t="s">
+        <v>109</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D22" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" t="s">
+        <v>62</v>
+      </c>
+      <c r="B23" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="D23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" t="s">
+        <v>117</v>
+      </c>
+      <c r="B24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C24" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D24" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25" t="s">
+        <v>121</v>
+      </c>
+      <c r="B25" t="s">
+        <v>122</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>119</v>
+      </c>
+      <c r="D25" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B26" t="s">
+        <v>112</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D26" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27" t="s">
+        <v>115</v>
+      </c>
+      <c r="B27" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29" s="34" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30" s="37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B30" s="37" t="s">
+        <v>107</v>
+      </c>
+      <c r="C30" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D30" s="11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B31" t="s">
+        <v>108</v>
+      </c>
+      <c r="C31">
+        <v>1</v>
+      </c>
+      <c r="D31" s="39" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32">
+        <v>2</v>
+      </c>
+      <c r="D32" s="33">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4">
+      <c r="A33" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B33" t="s">
+        <v>115</v>
+      </c>
+      <c r="C33">
+        <v>1</v>
+      </c>
+      <c r="D33" s="33">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4">
+      <c r="A34" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B34" t="s">
+        <v>111</v>
+      </c>
+      <c r="C34">
+        <v>1</v>
+      </c>
+      <c r="D34" s="33">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4">
+      <c r="A35" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35">
+        <v>3</v>
+      </c>
+      <c r="D35" s="33">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4">
+      <c r="A36" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" t="s">
+        <v>117</v>
+      </c>
+      <c r="C36">
+        <v>10</v>
+      </c>
+      <c r="D36" s="33">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4">
+      <c r="A37" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" t="s">
+        <v>121</v>
+      </c>
+      <c r="C37">
+        <v>2</v>
+      </c>
+      <c r="D37" s="33">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4">
+      <c r="A38" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" s="33">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4">
+      <c r="A39" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39">
+        <v>5</v>
+      </c>
+      <c r="D39" s="33">
+        <v>25000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4">
+      <c r="A40" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B40" t="s">
+        <v>121</v>
+      </c>
+      <c r="C40">
+        <v>1</v>
+      </c>
+      <c r="D40" s="33">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4">
+      <c r="A41" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B41" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41">
+        <v>2</v>
+      </c>
+      <c r="D41" s="33">
+        <v>1850000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4">
+      <c r="A42" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B42" t="s">
+        <v>115</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="D42" s="33">
+        <v>750000</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="1" max="1" width="30" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
+    <col min="4" max="4" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="16.8">
+    <row r="1" spans="1:4" ht="16.8">
       <c r="A1" s="10" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3" s="2" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1">
+    <row r="6" spans="1:4" ht="36" customHeight="1">
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
@@ -2352,7 +2985,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1">
+    <row r="7" spans="1:4" ht="36" customHeight="1">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
@@ -2361,86 +2994,36 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1">
+    <row r="8" spans="1:4" ht="36" customHeight="1">
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
       <c r="B8" s="16"/>
     </row>
-    <row r="10" spans="1:3">
+    <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="18"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="30" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3" ht="16.8">
-      <c r="A1" s="10" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="2" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="36" customHeight="1">
-      <c r="A6" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="B6" s="16"/>
-      <c r="C6" s="17" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" ht="36" customHeight="1">
-      <c r="A7" s="15" t="s">
-        <v>92</v>
-      </c>
-      <c r="B7" s="16"/>
-      <c r="C7" s="17" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3" ht="36" customHeight="1">
-      <c r="A8" s="15" t="s">
-        <v>94</v>
-      </c>
-      <c r="B8" s="16"/>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10" s="3" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11" s="18"/>
+    <row r="11" spans="1:4">
+      <c r="A11" s="18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="38"/>
+      <c r="B12" s="38"/>
+      <c r="C12" s="38"/>
+      <c r="D12" s="38"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="C13" s="12"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="C14" s="12"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="C15" s="12"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Normalisasi_SalesDB_Bagas.xlsx
+++ b/Normalisasi_SalesDB_Bagas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bagas\OneDrive\Desktop\Maganghub X MII\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41F3C872-455C-4302-8566-3BBF338C8E58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{997AACA4-CB77-4150-B27A-9A754DE33E20}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Petunjuk" sheetId="1" r:id="rId1"/>
@@ -83,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="363" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="145">
   <si>
     <t>Latihan Normalisasi SalesDB — dari data faktur (UNF) sampai 3NF</t>
   </si>
@@ -522,6 +522,36 @@
   </si>
   <si>
     <t xml:space="preserve">Tabel Pelanggan </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jakarta </t>
+  </si>
+  <si>
+    <t>Tabel Kategori</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan (PK)</t>
+  </si>
+  <si>
+    <t>Kode Kategori (PK)</t>
+  </si>
+  <si>
+    <t>Kode Kategori (FK)</t>
+  </si>
+  <si>
+    <t>Tabel Penjualan</t>
+  </si>
+  <si>
+    <t>Subtotal (Rp)</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan, Kode Kategori, Kode Produk , No Faktur, (No Faktur, Kode Produk)</t>
+  </si>
+  <si>
+    <t>Memisahkan Atribut Nama pelanggan, Memisahkan Atribut Kategori</t>
+  </si>
+  <si>
+    <t>Kode Pelanggan : Nama pelanggan, Email, Kota. Kode Kategori : Nama Kategori. Kode Produk : Nama Produk, Kode Kategori. No Faktur : Tangga, Kode Pelanggan. (No Faktur, Kode Produk) : Qty, Harga Satuan, Total Faktur.</t>
   </si>
 </sst>
 </file>
@@ -533,7 +563,7 @@
     <numFmt numFmtId="165" formatCode="[$Rp-421]#,##0.00"/>
     <numFmt numFmtId="166" formatCode="[$Rp-421]#,##0"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="16">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -624,13 +654,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="9">
@@ -777,9 +800,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -794,6 +814,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1340,8 +1363,8 @@
         <v>2150000</v>
       </c>
       <c r="O5" s="25"/>
-      <c r="P5" s="42"/>
-      <c r="Q5" s="42"/>
+      <c r="P5" s="41"/>
+      <c r="Q5" s="41"/>
     </row>
     <row r="6" spans="1:17" ht="48" customHeight="1">
       <c r="A6" s="12" t="s">
@@ -1564,10 +1587,10 @@
       <c r="Q10" s="26"/>
     </row>
     <row r="12" spans="1:17">
-      <c r="A12" s="41" t="s">
+      <c r="A12" s="40" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="41"/>
+      <c r="B12" s="40"/>
       <c r="C12" s="20"/>
       <c r="D12" s="20"/>
       <c r="E12" s="20"/>
@@ -1953,10 +1976,10 @@
       <c r="K12">
         <v>1</v>
       </c>
-      <c r="L12" s="31" t="s">
+      <c r="L12" s="38" t="s">
         <v>110</v>
       </c>
-      <c r="M12" s="31" t="s">
+      <c r="M12" s="38" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2476,7 +2499,7 @@
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="40" t="s">
+      <c r="B7" s="39" t="s">
         <v>132</v>
       </c>
       <c r="C7" s="17" t="s">
@@ -2502,7 +2525,7 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="37" t="s">
+      <c r="A12" s="28" t="s">
         <v>128</v>
       </c>
       <c r="B12" s="11" t="s">
@@ -2520,7 +2543,7 @@
       <c r="F12" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="38"/>
+      <c r="G12" s="37"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="12" t="s">
@@ -2654,7 +2677,7 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="37" t="s">
+      <c r="A21" s="28" t="s">
         <v>129</v>
       </c>
       <c r="B21" s="11" t="s">
@@ -2757,10 +2780,10 @@
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" s="37" t="s">
+      <c r="A30" s="28" t="s">
         <v>106</v>
       </c>
-      <c r="B30" s="37" t="s">
+      <c r="B30" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C30" s="11" t="s">
@@ -2780,7 +2803,7 @@
       <c r="C31">
         <v>1</v>
       </c>
-      <c r="D31" s="39" t="s">
+      <c r="D31" s="38" t="s">
         <v>110</v>
       </c>
     </row>
@@ -2947,13 +2970,14 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:D15"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="30" customWidth="1"/>
+    <col min="1" max="1" width="37" customWidth="1"/>
     <col min="2" max="2" width="60" customWidth="1"/>
     <col min="3" max="3" width="30" customWidth="1"/>
     <col min="4" max="4" width="19" customWidth="1"/>
+    <col min="5" max="5" width="14.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="16.8">
@@ -2980,16 +3004,20 @@
       <c r="A6" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="B6" s="16"/>
+      <c r="B6" s="39" t="s">
+        <v>142</v>
+      </c>
       <c r="C6" s="17" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="36" customHeight="1">
+    <row r="7" spans="1:4" ht="55.8" customHeight="1">
       <c r="A7" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="B7" s="16"/>
+      <c r="B7" s="39" t="s">
+        <v>144</v>
+      </c>
       <c r="C7" s="17" t="s">
         <v>93</v>
       </c>
@@ -2998,7 +3026,9 @@
       <c r="A8" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="16"/>
+      <c r="B8" s="16" t="s">
+        <v>143</v>
+      </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="3" t="s">
@@ -3011,21 +3041,501 @@
       </c>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="38"/>
-      <c r="B12" s="38"/>
-      <c r="C12" s="38"/>
-      <c r="D12" s="38"/>
+      <c r="A12" s="28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="13" spans="1:4">
-      <c r="C13" s="12"/>
+      <c r="A13" t="s">
+        <v>36</v>
+      </c>
+      <c r="B13" t="s">
+        <v>37</v>
+      </c>
+      <c r="C13" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="14" spans="1:4">
-      <c r="C14" s="12"/>
+      <c r="A14" t="s">
+        <v>47</v>
+      </c>
+      <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="C15" s="12"/>
+      <c r="A15" t="s">
+        <v>58</v>
+      </c>
+      <c r="B15" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="12" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" s="18" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" s="28" t="s">
+        <v>138</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>64</v>
+      </c>
+      <c r="B19" s="42" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>119</v>
+      </c>
+      <c r="B20" s="42" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="42" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="A23" s="18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="C24" s="11" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3">
+      <c r="A25" t="s">
+        <v>108</v>
+      </c>
+      <c r="B25" t="s">
+        <v>109</v>
+      </c>
+      <c r="C25" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
+      <c r="A26" t="s">
+        <v>62</v>
+      </c>
+      <c r="B26" t="s">
+        <v>63</v>
+      </c>
+      <c r="C26" s="19" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
+      <c r="A27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B27" t="s">
+        <v>118</v>
+      </c>
+      <c r="C27" s="19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" t="s">
+        <v>121</v>
+      </c>
+      <c r="B28" t="s">
+        <v>122</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3">
+      <c r="A29" t="s">
+        <v>111</v>
+      </c>
+      <c r="B29" t="s">
+        <v>112</v>
+      </c>
+      <c r="C29" s="19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
+      <c r="A30" t="s">
+        <v>115</v>
+      </c>
+      <c r="B30" t="s">
+        <v>116</v>
+      </c>
+      <c r="C30" s="19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
+      <c r="A32" s="18" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="28" t="s">
+        <v>128</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33" s="11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B34" s="13">
+        <v>46266</v>
+      </c>
+      <c r="C34" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="27" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35" s="13">
+        <v>46275</v>
+      </c>
+      <c r="C35" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="13">
+        <v>46277</v>
+      </c>
+      <c r="C36" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="B37" s="13">
+        <v>46280</v>
+      </c>
+      <c r="C37" s="19" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B38" s="13">
+        <v>46283</v>
+      </c>
+      <c r="C38" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="B39" s="13">
+        <v>46285</v>
+      </c>
+      <c r="C39" s="19" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="18" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="28" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="C42" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="D42" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="E42" s="11" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B43" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" s="19">
+        <v>1</v>
+      </c>
+      <c r="D43" s="38" t="s">
+        <v>110</v>
+      </c>
+      <c r="E43" s="38" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" s="19">
+        <v>2</v>
+      </c>
+      <c r="D44" s="33">
+        <v>150000</v>
+      </c>
+      <c r="E44" s="33">
+        <f>SUM(D44*C44)</f>
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B45" t="s">
+        <v>115</v>
+      </c>
+      <c r="C45" s="19">
+        <v>1</v>
+      </c>
+      <c r="D45" s="33">
+        <v>750000</v>
+      </c>
+      <c r="E45" s="33">
+        <f t="shared" ref="E45:E54" si="0">SUM(D45*C45)</f>
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B46" t="s">
+        <v>111</v>
+      </c>
+      <c r="C46" s="19">
+        <v>1</v>
+      </c>
+      <c r="D46" s="33">
+        <v>150000</v>
+      </c>
+      <c r="E46" s="33">
+        <f t="shared" si="0"/>
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" s="19">
+        <v>3</v>
+      </c>
+      <c r="D47" s="33">
+        <v>350000</v>
+      </c>
+      <c r="E47" s="33">
+        <f t="shared" si="0"/>
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="19">
+        <v>10</v>
+      </c>
+      <c r="D48" s="33">
+        <v>25000</v>
+      </c>
+      <c r="E48" s="33">
+        <f t="shared" si="0"/>
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B49" t="s">
+        <v>121</v>
+      </c>
+      <c r="C49" s="19">
+        <v>2</v>
+      </c>
+      <c r="D49" s="33">
+        <v>48000</v>
+      </c>
+      <c r="E49" s="33">
+        <f t="shared" si="0"/>
+        <v>96000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B50" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="19">
+        <v>1</v>
+      </c>
+      <c r="D50" s="33">
+        <v>375000</v>
+      </c>
+      <c r="E50" s="33">
+        <f t="shared" si="0"/>
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B51" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="19">
+        <v>5</v>
+      </c>
+      <c r="D51" s="33">
+        <v>25000</v>
+      </c>
+      <c r="E51" s="33">
+        <f t="shared" si="0"/>
+        <v>125000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B52" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="19">
+        <v>1</v>
+      </c>
+      <c r="D52" s="33">
+        <v>48000</v>
+      </c>
+      <c r="E52" s="33">
+        <f t="shared" si="0"/>
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B53" t="s">
+        <v>108</v>
+      </c>
+      <c r="C53" s="19">
+        <v>2</v>
+      </c>
+      <c r="D53" s="33">
+        <v>1850000</v>
+      </c>
+      <c r="E53" s="33">
+        <f t="shared" si="0"/>
+        <v>3700000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B54" t="s">
+        <v>115</v>
+      </c>
+      <c r="C54" s="19">
+        <v>1</v>
+      </c>
+      <c r="D54" s="33">
+        <v>750000</v>
+      </c>
+      <c r="E54" s="33">
+        <f t="shared" si="0"/>
+        <v>750000</v>
+      </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>